--- a/Results/TestCases/XLSX/buzz_TestCases.xlsx
+++ b/Results/TestCases/XLSX/buzz_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_BUZZ_02</t>
@@ -111,7 +111,7 @@
     <t>TC_BUZZ_07</t>
   </si>
   <si>
-    <t>Verify post textarea placeholder is What\</t>
+    <t>Verify post textarea placeholder is What's on your mind?</t>
   </si>
   <si>
     <t>TC_BUZZ_08</t>
@@ -249,7 +249,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -268,7 +268,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/buzz_TestCases.xlsx
+++ b/Results/TestCases/XLSX/buzz_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="107">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded. The user has navigated to the 'Buzz' module.</t>
+  </si>
+  <si>
+    <t>1. Perform the actions described in the test title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The header should equal 'Buzz'
+- The Buzz feed should be visible</t>
   </si>
   <si>
     <t>High</t>
@@ -81,18 +80,35 @@
     <t>Verify successful creation of new post</t>
   </si>
   <si>
+    <t>1. Enter post text and submit a new Buzz post</t>
+  </si>
+  <si>
+    <t>- It should be posted</t>
+  </si>
+  <si>
     <t>TC_BUZZ_03</t>
   </si>
   <si>
     <t>Verify feed filtering tabs are functional</t>
   </si>
   <si>
+    <t>1. Click the 'Most Liked Posts' tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The 'Most Recent Posts' tab should be visible
+- The 'Most Liked Posts' tab should be visible
+- The 'Most Commented Posts' tab should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_04</t>
   </si>
   <si>
     <t>Verify post button is disabled/ignored when post text is empty</t>
   </si>
   <si>
+    <t>- The final post count should be less than or equal to 'initialPostCount + 1'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -102,102 +118,162 @@
     <t>Verify Share Photos button is visible</t>
   </si>
   <si>
+    <t>- The 'Share Photos' element should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_06</t>
   </si>
   <si>
     <t>Verify Share Video button is visible</t>
   </si>
   <si>
+    <t>- The 'Share Video' element should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_07</t>
   </si>
   <si>
     <t>Verify post textarea placeholder is What's on your mind?</t>
   </si>
   <si>
+    <t>- The placeholder should equal 'What's on your mind?'</t>
+  </si>
+  <si>
     <t>TC_BUZZ_08</t>
   </si>
   <si>
     <t>Verify Most Recent Posts tab is visible by default</t>
   </si>
   <si>
+    <t>- The 'Most Recent Posts' tab should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_09</t>
   </si>
   <si>
     <t>Verify Most Commented Posts tab filters newsfeed</t>
   </si>
   <si>
+    <t>1. Click the 'Most Commented Posts' tab</t>
+  </si>
+  <si>
+    <t>- The 'Most Commented Posts' tab should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_10</t>
   </si>
   <si>
     <t>Verify newsfeed contains cards with profile avatars</t>
   </si>
   <si>
+    <t>- The avatar should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_11</t>
   </si>
   <si>
     <t>Verify user profile name link is visible on each post card</t>
   </si>
   <si>
+    <t>- The name link should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_12</t>
   </si>
   <si>
     <t>Verify timestamp elapsed duration text exists on post</t>
   </si>
   <si>
+    <t>- The time text should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_13</t>
   </si>
   <si>
     <t>Verify clicking Like button toggles like state</t>
   </si>
   <si>
+    <t>- The like btn should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_14</t>
   </si>
   <si>
     <t>Verify Comment icon button exists on feed posts</t>
   </si>
   <si>
+    <t>- The bi chat text fill element should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_15</t>
   </si>
   <si>
     <t>Verify Share icon button exists on feed posts</t>
   </si>
   <si>
+    <t>- The bi share fill element should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_16</t>
   </si>
   <si>
     <t>Verify Buzz page URL path is correct</t>
   </si>
   <si>
+    <t>- The page.url() should contain '/buzz/viewBuzz'</t>
+  </si>
+  <si>
     <t>TC_BUZZ_17</t>
   </si>
   <si>
     <t>Verify Share Photos button opens dialog pop-up</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the 'Share Photos' element
+2. Click the oxd dialog close button element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The modal should be visible
+- The modal should not be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_18</t>
   </si>
   <si>
     <t>Verify Share Video button opens dialog pop-up</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the 'Share Video' element
+2. Click the oxd dialog close button element</t>
+  </si>
+  <si>
     <t>TC_BUZZ_19</t>
   </si>
   <si>
     <t>Verify post options dropdown (dot menu) is functional</t>
   </si>
   <si>
+    <t>- The dot menu should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_20</t>
   </si>
   <si>
     <t>Verify feed scroll behavior is responsive</t>
   </si>
   <si>
+    <t>- The container should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_21</t>
   </si>
   <si>
     <t>Verify post content area does not overflow card width</t>
   </si>
   <si>
+    <t>- The post body should be present</t>
+  </si>
+  <si>
     <t>TC_BUZZ_22</t>
   </si>
   <si>
@@ -207,22 +283,64 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Click the 'Share Video' element
+2. Click the 'Share' element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The modal should be visible
+- The err should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_23</t>
   </si>
   <si>
     <t>Verify profile card elements are visible in left column of Buzz page</t>
   </si>
   <si>
+    <t>- The profile card should be visible</t>
+  </si>
+  <si>
     <t>TC_BUZZ_24</t>
   </si>
   <si>
     <t>Verify post textarea accepts special characters and emojis</t>
   </si>
   <si>
+    <t>- The value should equal 'emojiPost'</t>
+  </si>
+  <si>
     <t>TC_BUZZ_25</t>
   </si>
   <si>
     <t>Verify Buzz title in topbar matches breadcrumb text</t>
+  </si>
+  <si>
+    <t>- The title should contain the text 'Buzz'</t>
+  </si>
+  <si>
+    <t>TC_BUZZ_26</t>
+  </si>
+  <si>
+    <t>Verify creating a post with an extremely long text body does not crash the feed</t>
+  </si>
+  <si>
+    <t>TC_BUZZ_27</t>
+  </si>
+  <si>
+    <t>Verify a newly created post appears near the top of the Most Recent Posts feed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- It should be posted
+- The found near top should equal 'true'</t>
+  </si>
+  <si>
+    <t>TC_BUZZ_28</t>
+  </si>
+  <si>
+    <t>Verify a script tag entered in the post textarea is rendered as plain text and not executed</t>
+  </si>
+  <si>
+    <t>- The dialog fired should equal 'false'</t>
   </si>
 </sst>
 </file>
@@ -660,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -766,10 +884,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>18</v>
@@ -780,7 +898,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,22 +907,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -815,7 +933,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,13 +942,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -839,10 +957,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -850,7 +968,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,13 +977,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -874,10 +992,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,7 +1003,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,13 +1012,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -909,10 +1027,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +1038,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,13 +1047,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
@@ -944,10 +1062,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +1073,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,13 +1082,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -979,10 +1097,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -990,7 +1108,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,25 +1117,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1025,7 +1143,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,13 +1152,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1049,10 +1167,10 @@
         <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1060,7 +1178,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,13 +1187,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1084,10 +1202,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1095,7 +1213,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,13 +1222,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1119,10 +1237,10 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1248,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,13 +1257,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1154,10 +1272,10 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1165,7 +1283,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,13 +1292,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1189,10 +1307,10 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1200,7 +1318,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,13 +1327,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1224,10 +1342,10 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1235,7 +1353,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,13 +1362,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1259,10 +1377,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1270,7 +1388,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,25 +1397,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1305,7 +1423,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,25 +1432,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1340,7 +1458,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,13 +1467,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1364,10 +1482,10 @@
         <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1375,7 +1493,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,13 +1502,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1399,10 +1517,10 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1410,7 +1528,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1537,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1434,10 +1552,10 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1445,7 +1563,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,25 +1572,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1598,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,13 +1607,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1504,10 +1622,10 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1633,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,13 +1642,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1539,10 +1657,10 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1668,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,13 +1677,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1574,12 +1692,117 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Results/TestCases/XLSX/buzz_TestCases.xlsx
+++ b/Results/TestCases/XLSX/buzz_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="108">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -71,7 +71,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>PASSED</t>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_BUZZ_02</t>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>- The name link should be present</t>
+  </si>
+  <si>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_BUZZ_12</t>
@@ -347,7 +350,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -367,12 +370,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +391,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF7919"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -428,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -437,6 +451,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1207,13 +1224,13 @@
       <c r="J12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+      <c r="K12" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1222,13 +1239,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1237,18 +1254,18 @@
         <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+      <c r="K13" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1257,13 +1274,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1272,18 +1289,18 @@
         <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+      <c r="K14" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1292,13 +1309,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1307,18 +1324,18 @@
         <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+      <c r="K15" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1327,13 +1344,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1342,18 +1359,18 @@
         <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+      <c r="K16" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1362,13 +1379,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
@@ -1377,18 +1394,18 @@
         <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+      <c r="K17" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1397,68 +1414,68 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+      <c r="K18" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="J19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+      <c r="K19" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1467,13 +1484,13 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1482,18 +1499,18 @@
         <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+      <c r="K20" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1502,13 +1519,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1517,18 +1534,18 @@
         <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+      <c r="K21" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1537,13 +1554,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1552,18 +1569,18 @@
         <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+      <c r="K22" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1572,33 +1589,33 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+      <c r="K23" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1607,13 +1624,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1622,18 +1639,18 @@
         <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+      <c r="K24" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1642,13 +1659,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1657,18 +1674,18 @@
         <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+      <c r="K25" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1677,13 +1694,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1692,18 +1709,18 @@
         <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+      <c r="K26" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
@@ -1712,13 +1729,13 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -1732,13 +1749,13 @@
       <c r="J27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>19</v>
+      <c r="K27" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
@@ -1747,13 +1764,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -1762,18 +1779,18 @@
         <v>22</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>19</v>
+      <c r="K28" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
@@ -1782,13 +1799,13 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
@@ -1797,13 +1814,13 @@
         <v>22</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>19</v>
+      <c r="K29" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
